--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2EEFE75-8A85-4E0E-80B3-AF3379422649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE947610-9DE2-42B9-B1A1-0732B960C149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="2310" windowWidth="20565" windowHeight="11295" xr2:uid="{14BAFB78-9D84-4003-B39B-9AAF5B82A536}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{14BAFB78-9D84-4003-B39B-9AAF5B82A536}"/>
   </bookViews>
   <sheets>
     <sheet name="เวอร์เนีย 200.." sheetId="5" r:id="rId1"/>
@@ -341,84 +341,84 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1468,632 +1468,713 @@
     <col min="16131" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="31" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22"/>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="31"/>
-      <c r="AD1" s="31"/>
-      <c r="AE1" s="31"/>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
+      <c r="AC1" s="23"/>
+      <c r="AD1" s="23"/>
+      <c r="AE1" s="23"/>
+      <c r="AF1" s="23"/>
+      <c r="AG1" s="23"/>
     </row>
-    <row r="2" spans="1:33" s="27" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="31" t="s">
+    <row r="2" spans="1:33" s="16" customFormat="1" ht="25.5" customHeight="1">
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+      <c r="AA2" s="22"/>
+      <c r="AB2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
     </row>
-    <row r="3" spans="1:33" s="27" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="28"/>
-      <c r="AG3" s="28"/>
+    <row r="3" spans="1:33" s="16" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="19"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+      <c r="Y3" s="17"/>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+      <c r="AF3" s="17"/>
+      <c r="AG3" s="17"/>
     </row>
-    <row r="4" spans="1:33" s="15" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:33" s="9" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
     </row>
-    <row r="5" spans="1:33" s="15" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="21">
+    <row r="5" spans="1:33" s="9" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="15">
         <v>1</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="15">
         <v>2</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="15">
         <v>3</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="15">
         <v>4</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="15">
         <v>5</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="15">
         <v>6</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="15">
         <v>7</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="15">
         <v>8</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="15">
         <v>9</v>
       </c>
-      <c r="L5" s="21">
+      <c r="L5" s="15">
         <v>10</v>
       </c>
-      <c r="M5" s="21">
+      <c r="M5" s="15">
         <v>11</v>
       </c>
-      <c r="N5" s="21">
+      <c r="N5" s="15">
         <v>12</v>
       </c>
-      <c r="O5" s="21">
+      <c r="O5" s="15">
         <v>13</v>
       </c>
-      <c r="P5" s="21">
+      <c r="P5" s="15">
         <v>14</v>
       </c>
-      <c r="Q5" s="21">
+      <c r="Q5" s="15">
         <v>15</v>
       </c>
-      <c r="R5" s="21">
+      <c r="R5" s="15">
         <v>16</v>
       </c>
-      <c r="S5" s="21">
+      <c r="S5" s="15">
         <v>17</v>
       </c>
-      <c r="T5" s="21">
+      <c r="T5" s="15">
         <v>18</v>
       </c>
-      <c r="U5" s="21">
+      <c r="U5" s="15">
         <v>19</v>
       </c>
-      <c r="V5" s="21">
+      <c r="V5" s="15">
         <v>20</v>
       </c>
-      <c r="W5" s="21">
+      <c r="W5" s="15">
         <v>21</v>
       </c>
-      <c r="X5" s="21">
+      <c r="X5" s="15">
         <v>22</v>
       </c>
-      <c r="Y5" s="21">
+      <c r="Y5" s="15">
         <v>23</v>
       </c>
-      <c r="Z5" s="21">
+      <c r="Z5" s="15">
         <v>24</v>
       </c>
-      <c r="AA5" s="21">
+      <c r="AA5" s="15">
         <v>25</v>
       </c>
-      <c r="AB5" s="21">
+      <c r="AB5" s="15">
         <v>26</v>
       </c>
-      <c r="AC5" s="21">
+      <c r="AC5" s="15">
         <v>27</v>
       </c>
-      <c r="AD5" s="21">
+      <c r="AD5" s="15">
         <v>28</v>
       </c>
-      <c r="AE5" s="21">
+      <c r="AE5" s="15">
         <v>29</v>
       </c>
-      <c r="AF5" s="21">
+      <c r="AF5" s="15">
         <v>30</v>
       </c>
-      <c r="AG5" s="21">
+      <c r="AG5" s="15">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="20">
+    <row r="6" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A6" s="14">
         <v>1</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
+      <c r="AA6" s="10"/>
+      <c r="AB6" s="10"/>
+      <c r="AC6" s="10"/>
+      <c r="AD6" s="10"/>
+      <c r="AE6" s="10"/>
+      <c r="AF6" s="10"/>
+      <c r="AG6" s="10"/>
     </row>
-    <row r="7" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="18">
+    <row r="7" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="12">
         <v>2</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="16"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="16"/>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
     </row>
-    <row r="8" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="18">
+    <row r="8" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A8" s="12">
         <v>3</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
+      <c r="AA8" s="10"/>
+      <c r="AB8" s="10"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="10"/>
+      <c r="AE8" s="10"/>
+      <c r="AF8" s="10"/>
+      <c r="AG8" s="10"/>
     </row>
-    <row r="9" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A9" s="18">
+    <row r="9" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
-      <c r="AD9" s="16"/>
-      <c r="AE9" s="16"/>
-      <c r="AF9" s="16"/>
-      <c r="AG9" s="16"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
+      <c r="AA9" s="10"/>
+      <c r="AB9" s="10"/>
+      <c r="AC9" s="10"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="10"/>
+      <c r="AF9" s="10"/>
+      <c r="AG9" s="10"/>
     </row>
-    <row r="10" spans="1:33" s="15" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A10" s="18">
+    <row r="10" spans="1:33" s="9" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A10" s="12">
         <v>5</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-      <c r="AB10" s="16"/>
-      <c r="AC10" s="16"/>
-      <c r="AD10" s="16"/>
-      <c r="AE10" s="16"/>
-      <c r="AF10" s="16"/>
-      <c r="AG10" s="16"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
+      <c r="AA10" s="10"/>
+      <c r="AB10" s="10"/>
+      <c r="AC10" s="10"/>
+      <c r="AD10" s="10"/>
+      <c r="AE10" s="10"/>
+      <c r="AF10" s="10"/>
+      <c r="AG10" s="10"/>
     </row>
-    <row r="11" spans="1:33" s="1" customFormat="1" ht="22.5" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="12"/>
-      <c r="W11" s="12"/>
-      <c r="X11" s="12"/>
-      <c r="Y11" s="12"/>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="12"/>
-      <c r="AC11" s="12"/>
-      <c r="AD11" s="12"/>
-      <c r="AE11" s="12"/>
-      <c r="AF11" s="12"/>
-      <c r="AG11" s="12"/>
+    <row r="11" spans="1:33" ht="22.5" customHeight="1">
+      <c r="A11" s="8"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
     </row>
-    <row r="12" spans="1:33" s="1" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B12" s="10"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="9"/>
-      <c r="AG12" s="9"/>
+    <row r="12" spans="1:33" ht="22.5" customHeight="1">
+      <c r="B12" s="6"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
     </row>
-    <row r="13" spans="1:33" s="1" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B13" s="10"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="11"/>
-      <c r="Z13" s="11"/>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="11"/>
-      <c r="AG13" s="11"/>
+    <row r="13" spans="1:33" ht="22.5" customHeight="1">
+      <c r="B13" s="6"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="29"/>
+      <c r="AG13" s="29"/>
     </row>
-    <row r="14" spans="1:33" s="1" customFormat="1" ht="22.5" customHeight="1">
-      <c r="B14" s="10"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
-      <c r="S14" s="9"/>
-      <c r="T14" s="9"/>
-      <c r="U14" s="9"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="9"/>
-      <c r="X14" s="9"/>
-      <c r="Y14" s="9"/>
-      <c r="Z14" s="9"/>
-      <c r="AA14" s="9"/>
-      <c r="AB14" s="9"/>
-      <c r="AC14" s="9"/>
-      <c r="AD14" s="9"/>
-      <c r="AE14" s="9"/>
-      <c r="AF14" s="9"/>
-      <c r="AG14" s="9"/>
+    <row r="14" spans="1:33" ht="22.5" customHeight="1">
+      <c r="B14" s="6"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
     </row>
-    <row r="15" spans="1:33" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="1:33" ht="19.5" customHeight="1">
+      <c r="B15" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="1" customFormat="1" ht="185.25" customHeight="1">
-      <c r="B16" s="7"/>
+    <row r="16" spans="1:33" ht="185.25" customHeight="1">
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="32"/>
+      <c r="AG16" s="32"/>
     </row>
-    <row r="17" spans="3:33" s="1" customFormat="1" ht="23.25" customHeight="1"/>
-    <row r="18" spans="3:33" s="1" customFormat="1" ht="21">
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="5"/>
-      <c r="AG18" s="5"/>
+    <row r="17" spans="3:33" ht="23.25" customHeight="1"/>
+    <row r="18" spans="3:33" ht="21">
+      <c r="AA18" s="4"/>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
     </row>
-    <row r="19" spans="3:33" s="1" customFormat="1" ht="29.25" customHeight="1">
-      <c r="AC19" s="4" t="s">
+    <row r="19" spans="3:33" ht="29.25" customHeight="1">
+      <c r="AC19" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="AD19" s="4"/>
-      <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-      <c r="AG19" s="4"/>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
     </row>
-    <row r="20" spans="3:33" s="1" customFormat="1" ht="14.25" customHeight="1">
+    <row r="20" spans="3:33" ht="14.25" customHeight="1">
       <c r="C20" s="3"/>
       <c r="AG20" s="2" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="71">
+    <mergeCell ref="AC19:AG19"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="B16:AG16"/>
+    <mergeCell ref="AC18:AG18"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="AC11:AC12"/>
+    <mergeCell ref="AD11:AD12"/>
+    <mergeCell ref="AE11:AE12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
     <mergeCell ref="X11:X12"/>
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="N11:N12"/>
@@ -2104,56 +2185,7 @@
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:I12"/>
-    <mergeCell ref="AC11:AC12"/>
-    <mergeCell ref="AD11:AD12"/>
-    <mergeCell ref="AE11:AE12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="Z11:Z12"/>
     <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AC18:AG18"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="AC19:AG19"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -330,7 +330,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -429,6 +429,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1763,8 +1766,16 @@
       <c r="AB6" s="24" t="n"/>
       <c r="AC6" s="24" t="n"/>
       <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="24" t="n"/>
-      <c r="AF6" s="24" t="n"/>
+      <c r="AE6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="24" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1804,8 +1815,16 @@
       <c r="AB7" s="24" t="n"/>
       <c r="AC7" s="24" t="n"/>
       <c r="AD7" s="24" t="n"/>
-      <c r="AE7" s="24" t="n"/>
-      <c r="AF7" s="24" t="n"/>
+      <c r="AE7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="24" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1845,8 +1864,16 @@
       <c r="AB8" s="24" t="n"/>
       <c r="AC8" s="24" t="n"/>
       <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="24" t="n"/>
-      <c r="AF8" s="24" t="n"/>
+      <c r="AE8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="24" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1886,8 +1913,16 @@
       <c r="AB9" s="24" t="n"/>
       <c r="AC9" s="24" t="n"/>
       <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="24" t="n"/>
-      <c r="AF9" s="24" t="n"/>
+      <c r="AE9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="24" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="9">
@@ -1927,8 +1962,16 @@
       <c r="AB10" s="24" t="n"/>
       <c r="AC10" s="24" t="n"/>
       <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="24" t="n"/>
-      <c r="AF10" s="24" t="n"/>
+      <c r="AE10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="24" t="n"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
@@ -1962,8 +2005,16 @@
       <c r="AB11" s="38" t="n"/>
       <c r="AC11" s="38" t="n"/>
       <c r="AD11" s="38" t="n"/>
-      <c r="AE11" s="38" t="n"/>
-      <c r="AF11" s="38" t="n"/>
+      <c r="AE11" s="40" t="inlineStr">
+        <is>
+          <t>พนารัตน์</t>
+        </is>
+      </c>
+      <c r="AF11" s="40" t="inlineStr">
+        <is>
+          <t>พนารัตน์</t>
+        </is>
+      </c>
       <c r="AG11" s="38" t="n"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
@@ -2076,7 +2127,7 @@
       </c>
     </row>
     <row r="16" ht="185.25" customHeight="1">
-      <c r="B16" s="32" t="n"/>
+      <c r="B16" s="32" t="inlineStr"/>
     </row>
     <row r="17" ht="23.25" customHeight="1"/>
     <row r="18" ht="21" customHeight="1">
@@ -2107,8 +2158,8 @@
   <mergeCells count="71">
     <mergeCell ref="S11:S12"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="J13:J14"/>
     <mergeCell ref="U11:U12"/>
-    <mergeCell ref="J13:J14"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="R13:R14"/>
     <mergeCell ref="AD13:AD14"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -330,7 +330,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -431,6 +431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1738,45 +1741,37 @@
           <t>ตรวจดูสภาพของเวอร์เนียพร้อมใช้งานหรือไม่</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="24" t="n"/>
-      <c r="F6" s="24" t="n"/>
-      <c r="G6" s="24" t="n"/>
-      <c r="H6" s="24" t="n"/>
-      <c r="I6" s="24" t="n"/>
-      <c r="J6" s="24" t="n"/>
-      <c r="K6" s="24" t="n"/>
-      <c r="L6" s="24" t="n"/>
-      <c r="M6" s="24" t="n"/>
-      <c r="N6" s="24" t="n"/>
-      <c r="O6" s="24" t="n"/>
-      <c r="P6" s="24" t="n"/>
-      <c r="Q6" s="24" t="n"/>
-      <c r="R6" s="24" t="n"/>
-      <c r="S6" s="24" t="n"/>
-      <c r="T6" s="24" t="n"/>
-      <c r="U6" s="24" t="n"/>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="24" t="n"/>
-      <c r="X6" s="24" t="n"/>
-      <c r="Y6" s="24" t="n"/>
-      <c r="Z6" s="24" t="n"/>
-      <c r="AA6" s="24" t="n"/>
-      <c r="AB6" s="24" t="n"/>
-      <c r="AC6" s="24" t="n"/>
-      <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="24" t="n"/>
+      <c r="C6" s="24" t="inlineStr"/>
+      <c r="D6" s="24" t="inlineStr"/>
+      <c r="E6" s="24" t="inlineStr"/>
+      <c r="F6" s="24" t="inlineStr"/>
+      <c r="G6" s="24" t="inlineStr"/>
+      <c r="H6" s="24" t="inlineStr"/>
+      <c r="I6" s="24" t="inlineStr"/>
+      <c r="J6" s="24" t="inlineStr"/>
+      <c r="K6" s="24" t="inlineStr"/>
+      <c r="L6" s="24" t="inlineStr"/>
+      <c r="M6" s="24" t="inlineStr"/>
+      <c r="N6" s="24" t="inlineStr"/>
+      <c r="O6" s="24" t="inlineStr"/>
+      <c r="P6" s="24" t="inlineStr"/>
+      <c r="Q6" s="24" t="inlineStr"/>
+      <c r="R6" s="24" t="inlineStr"/>
+      <c r="S6" s="24" t="inlineStr"/>
+      <c r="T6" s="24" t="inlineStr"/>
+      <c r="U6" s="24" t="inlineStr"/>
+      <c r="V6" s="24" t="inlineStr"/>
+      <c r="W6" s="24" t="inlineStr"/>
+      <c r="X6" s="24" t="inlineStr"/>
+      <c r="Y6" s="24" t="inlineStr"/>
+      <c r="Z6" s="24" t="inlineStr"/>
+      <c r="AA6" s="24" t="inlineStr"/>
+      <c r="AB6" s="24" t="inlineStr"/>
+      <c r="AC6" s="24" t="inlineStr"/>
+      <c r="AD6" s="24" t="inlineStr"/>
+      <c r="AE6" s="24" t="inlineStr"/>
+      <c r="AF6" s="24" t="inlineStr"/>
+      <c r="AG6" s="24" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A7" s="12" t="n">
@@ -1787,45 +1782,37 @@
           <t>ตรวจดู BATTERRY อ่อนหรือไม่</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n"/>
-      <c r="D7" s="24" t="n"/>
-      <c r="E7" s="24" t="n"/>
-      <c r="F7" s="24" t="n"/>
-      <c r="G7" s="24" t="n"/>
-      <c r="H7" s="24" t="n"/>
-      <c r="I7" s="24" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="24" t="n"/>
-      <c r="L7" s="24" t="n"/>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="24" t="n"/>
-      <c r="O7" s="24" t="n"/>
-      <c r="P7" s="24" t="n"/>
-      <c r="Q7" s="24" t="n"/>
-      <c r="R7" s="24" t="n"/>
-      <c r="S7" s="24" t="n"/>
-      <c r="T7" s="24" t="n"/>
-      <c r="U7" s="24" t="n"/>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="24" t="n"/>
-      <c r="X7" s="24" t="n"/>
-      <c r="Y7" s="24" t="n"/>
-      <c r="Z7" s="24" t="n"/>
-      <c r="AA7" s="24" t="n"/>
-      <c r="AB7" s="24" t="n"/>
-      <c r="AC7" s="24" t="n"/>
-      <c r="AD7" s="24" t="n"/>
-      <c r="AE7" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="24" t="n"/>
+      <c r="C7" s="24" t="inlineStr"/>
+      <c r="D7" s="24" t="inlineStr"/>
+      <c r="E7" s="24" t="inlineStr"/>
+      <c r="F7" s="24" t="inlineStr"/>
+      <c r="G7" s="24" t="inlineStr"/>
+      <c r="H7" s="24" t="inlineStr"/>
+      <c r="I7" s="24" t="inlineStr"/>
+      <c r="J7" s="24" t="inlineStr"/>
+      <c r="K7" s="24" t="inlineStr"/>
+      <c r="L7" s="24" t="inlineStr"/>
+      <c r="M7" s="24" t="inlineStr"/>
+      <c r="N7" s="24" t="inlineStr"/>
+      <c r="O7" s="24" t="inlineStr"/>
+      <c r="P7" s="24" t="inlineStr"/>
+      <c r="Q7" s="24" t="inlineStr"/>
+      <c r="R7" s="24" t="inlineStr"/>
+      <c r="S7" s="24" t="inlineStr"/>
+      <c r="T7" s="24" t="inlineStr"/>
+      <c r="U7" s="24" t="inlineStr"/>
+      <c r="V7" s="24" t="inlineStr"/>
+      <c r="W7" s="24" t="inlineStr"/>
+      <c r="X7" s="24" t="inlineStr"/>
+      <c r="Y7" s="24" t="inlineStr"/>
+      <c r="Z7" s="24" t="inlineStr"/>
+      <c r="AA7" s="24" t="inlineStr"/>
+      <c r="AB7" s="24" t="inlineStr"/>
+      <c r="AC7" s="24" t="inlineStr"/>
+      <c r="AD7" s="24" t="inlineStr"/>
+      <c r="AE7" s="24" t="inlineStr"/>
+      <c r="AF7" s="24" t="inlineStr"/>
+      <c r="AG7" s="24" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A8" s="12" t="n">
@@ -1836,45 +1823,37 @@
           <t>ตรวจสอบการสไลด์ต้องไม่ติดขัด</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-      <c r="I8" s="24" t="n"/>
-      <c r="J8" s="24" t="n"/>
-      <c r="K8" s="24" t="n"/>
-      <c r="L8" s="24" t="n"/>
-      <c r="M8" s="24" t="n"/>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n"/>
-      <c r="P8" s="24" t="n"/>
-      <c r="Q8" s="24" t="n"/>
-      <c r="R8" s="24" t="n"/>
-      <c r="S8" s="24" t="n"/>
-      <c r="T8" s="24" t="n"/>
-      <c r="U8" s="24" t="n"/>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="24" t="n"/>
-      <c r="X8" s="24" t="n"/>
-      <c r="Y8" s="24" t="n"/>
-      <c r="Z8" s="24" t="n"/>
-      <c r="AA8" s="24" t="n"/>
-      <c r="AB8" s="24" t="n"/>
-      <c r="AC8" s="24" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="n"/>
+      <c r="C8" s="24" t="inlineStr"/>
+      <c r="D8" s="24" t="inlineStr"/>
+      <c r="E8" s="24" t="inlineStr"/>
+      <c r="F8" s="24" t="inlineStr"/>
+      <c r="G8" s="24" t="inlineStr"/>
+      <c r="H8" s="24" t="inlineStr"/>
+      <c r="I8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="inlineStr"/>
+      <c r="K8" s="24" t="inlineStr"/>
+      <c r="L8" s="24" t="inlineStr"/>
+      <c r="M8" s="24" t="inlineStr"/>
+      <c r="N8" s="24" t="inlineStr"/>
+      <c r="O8" s="24" t="inlineStr"/>
+      <c r="P8" s="24" t="inlineStr"/>
+      <c r="Q8" s="24" t="inlineStr"/>
+      <c r="R8" s="24" t="inlineStr"/>
+      <c r="S8" s="24" t="inlineStr"/>
+      <c r="T8" s="24" t="inlineStr"/>
+      <c r="U8" s="24" t="inlineStr"/>
+      <c r="V8" s="24" t="inlineStr"/>
+      <c r="W8" s="24" t="inlineStr"/>
+      <c r="X8" s="24" t="inlineStr"/>
+      <c r="Y8" s="24" t="inlineStr"/>
+      <c r="Z8" s="24" t="inlineStr"/>
+      <c r="AA8" s="24" t="inlineStr"/>
+      <c r="AB8" s="24" t="inlineStr"/>
+      <c r="AC8" s="24" t="inlineStr"/>
+      <c r="AD8" s="24" t="inlineStr"/>
+      <c r="AE8" s="24" t="inlineStr"/>
+      <c r="AF8" s="24" t="inlineStr"/>
+      <c r="AG8" s="24" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A9" s="12" t="n">
@@ -1885,45 +1864,37 @@
           <t>ตรวจสอบที่คีบตรงปลายที่ใช้วัดชิ้นงาน เช็คว่ามีรอยบิ่น หรือสึกหล่อหรือไม่</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="24" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="24" t="n"/>
-      <c r="K9" s="24" t="n"/>
-      <c r="L9" s="24" t="n"/>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="24" t="n"/>
-      <c r="O9" s="24" t="n"/>
-      <c r="P9" s="24" t="n"/>
-      <c r="Q9" s="24" t="n"/>
-      <c r="R9" s="24" t="n"/>
-      <c r="S9" s="24" t="n"/>
-      <c r="T9" s="24" t="n"/>
-      <c r="U9" s="24" t="n"/>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="24" t="n"/>
-      <c r="X9" s="24" t="n"/>
-      <c r="Y9" s="24" t="n"/>
-      <c r="Z9" s="24" t="n"/>
-      <c r="AA9" s="24" t="n"/>
-      <c r="AB9" s="24" t="n"/>
-      <c r="AC9" s="24" t="n"/>
-      <c r="AD9" s="24" t="n"/>
-      <c r="AE9" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="24" t="n"/>
+      <c r="C9" s="24" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr"/>
+      <c r="E9" s="24" t="inlineStr"/>
+      <c r="F9" s="24" t="inlineStr"/>
+      <c r="G9" s="24" t="inlineStr"/>
+      <c r="H9" s="24" t="inlineStr"/>
+      <c r="I9" s="24" t="inlineStr"/>
+      <c r="J9" s="24" t="inlineStr"/>
+      <c r="K9" s="24" t="inlineStr"/>
+      <c r="L9" s="24" t="inlineStr"/>
+      <c r="M9" s="24" t="inlineStr"/>
+      <c r="N9" s="24" t="inlineStr"/>
+      <c r="O9" s="24" t="inlineStr"/>
+      <c r="P9" s="24" t="inlineStr"/>
+      <c r="Q9" s="24" t="inlineStr"/>
+      <c r="R9" s="24" t="inlineStr"/>
+      <c r="S9" s="24" t="inlineStr"/>
+      <c r="T9" s="24" t="inlineStr"/>
+      <c r="U9" s="24" t="inlineStr"/>
+      <c r="V9" s="24" t="inlineStr"/>
+      <c r="W9" s="24" t="inlineStr"/>
+      <c r="X9" s="24" t="inlineStr"/>
+      <c r="Y9" s="24" t="inlineStr"/>
+      <c r="Z9" s="24" t="inlineStr"/>
+      <c r="AA9" s="24" t="inlineStr"/>
+      <c r="AB9" s="24" t="inlineStr"/>
+      <c r="AC9" s="24" t="inlineStr"/>
+      <c r="AD9" s="24" t="inlineStr"/>
+      <c r="AE9" s="24" t="inlineStr"/>
+      <c r="AF9" s="24" t="inlineStr"/>
+      <c r="AG9" s="24" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="9">
       <c r="A10" s="12" t="n">
@@ -1934,88 +1905,72 @@
           <t>หลังเลิกงานต้องปิดสวิตส์ทุกครั้ง</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="24" t="n"/>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n"/>
-      <c r="L10" s="24" t="n"/>
-      <c r="M10" s="24" t="n"/>
-      <c r="N10" s="24" t="n"/>
-      <c r="O10" s="24" t="n"/>
-      <c r="P10" s="24" t="n"/>
-      <c r="Q10" s="24" t="n"/>
-      <c r="R10" s="24" t="n"/>
-      <c r="S10" s="24" t="n"/>
-      <c r="T10" s="24" t="n"/>
-      <c r="U10" s="24" t="n"/>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="24" t="n"/>
-      <c r="X10" s="24" t="n"/>
-      <c r="Y10" s="24" t="n"/>
-      <c r="Z10" s="24" t="n"/>
-      <c r="AA10" s="24" t="n"/>
-      <c r="AB10" s="24" t="n"/>
-      <c r="AC10" s="24" t="n"/>
-      <c r="AD10" s="24" t="n"/>
-      <c r="AE10" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="24" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="24" t="n"/>
+      <c r="C10" s="24" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr"/>
+      <c r="E10" s="24" t="inlineStr"/>
+      <c r="F10" s="24" t="inlineStr"/>
+      <c r="G10" s="24" t="inlineStr"/>
+      <c r="H10" s="24" t="inlineStr"/>
+      <c r="I10" s="24" t="inlineStr"/>
+      <c r="J10" s="24" t="inlineStr"/>
+      <c r="K10" s="24" t="inlineStr"/>
+      <c r="L10" s="24" t="inlineStr"/>
+      <c r="M10" s="24" t="inlineStr"/>
+      <c r="N10" s="24" t="inlineStr"/>
+      <c r="O10" s="24" t="inlineStr"/>
+      <c r="P10" s="24" t="inlineStr"/>
+      <c r="Q10" s="24" t="inlineStr"/>
+      <c r="R10" s="24" t="inlineStr"/>
+      <c r="S10" s="24" t="inlineStr"/>
+      <c r="T10" s="24" t="inlineStr"/>
+      <c r="U10" s="24" t="inlineStr"/>
+      <c r="V10" s="24" t="inlineStr"/>
+      <c r="W10" s="24" t="inlineStr"/>
+      <c r="X10" s="24" t="inlineStr"/>
+      <c r="Y10" s="24" t="inlineStr"/>
+      <c r="Z10" s="24" t="inlineStr"/>
+      <c r="AA10" s="24" t="inlineStr"/>
+      <c r="AB10" s="24" t="inlineStr"/>
+      <c r="AC10" s="24" t="inlineStr"/>
+      <c r="AD10" s="24" t="inlineStr"/>
+      <c r="AE10" s="24" t="inlineStr"/>
+      <c r="AF10" s="24" t="inlineStr"/>
+      <c r="AG10" s="24" t="inlineStr"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="8" t="n"/>
       <c r="B11" s="7" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="38" t="n"/>
-      <c r="F11" s="38" t="n"/>
-      <c r="G11" s="38" t="n"/>
-      <c r="H11" s="38" t="n"/>
-      <c r="I11" s="38" t="n"/>
-      <c r="J11" s="38" t="n"/>
-      <c r="K11" s="38" t="n"/>
-      <c r="L11" s="38" t="n"/>
-      <c r="M11" s="38" t="n"/>
-      <c r="N11" s="38" t="n"/>
-      <c r="O11" s="38" t="n"/>
-      <c r="P11" s="38" t="n"/>
-      <c r="Q11" s="38" t="n"/>
-      <c r="R11" s="38" t="n"/>
-      <c r="S11" s="38" t="n"/>
-      <c r="T11" s="38" t="n"/>
-      <c r="U11" s="38" t="n"/>
-      <c r="V11" s="38" t="n"/>
-      <c r="W11" s="38" t="n"/>
-      <c r="X11" s="38" t="n"/>
-      <c r="Y11" s="38" t="n"/>
-      <c r="Z11" s="38" t="n"/>
-      <c r="AA11" s="38" t="n"/>
-      <c r="AB11" s="38" t="n"/>
-      <c r="AC11" s="38" t="n"/>
-      <c r="AD11" s="38" t="n"/>
-      <c r="AE11" s="40" t="inlineStr">
-        <is>
-          <t>พนารัตน์</t>
-        </is>
-      </c>
-      <c r="AF11" s="40" t="inlineStr">
-        <is>
-          <t>พนารัตน์</t>
-        </is>
-      </c>
-      <c r="AG11" s="38" t="n"/>
+      <c r="C11" s="38" t="inlineStr"/>
+      <c r="D11" s="38" t="inlineStr"/>
+      <c r="E11" s="38" t="inlineStr"/>
+      <c r="F11" s="38" t="inlineStr"/>
+      <c r="G11" s="38" t="inlineStr"/>
+      <c r="H11" s="38" t="inlineStr"/>
+      <c r="I11" s="38" t="inlineStr"/>
+      <c r="J11" s="38" t="inlineStr"/>
+      <c r="K11" s="38" t="inlineStr"/>
+      <c r="L11" s="38" t="inlineStr"/>
+      <c r="M11" s="38" t="inlineStr"/>
+      <c r="N11" s="38" t="inlineStr"/>
+      <c r="O11" s="38" t="inlineStr"/>
+      <c r="P11" s="38" t="inlineStr"/>
+      <c r="Q11" s="38" t="inlineStr"/>
+      <c r="R11" s="38" t="inlineStr"/>
+      <c r="S11" s="38" t="inlineStr"/>
+      <c r="T11" s="38" t="inlineStr"/>
+      <c r="U11" s="38" t="inlineStr"/>
+      <c r="V11" s="38" t="inlineStr"/>
+      <c r="W11" s="38" t="inlineStr"/>
+      <c r="X11" s="38" t="inlineStr"/>
+      <c r="Y11" s="38" t="inlineStr"/>
+      <c r="Z11" s="38" t="inlineStr"/>
+      <c r="AA11" s="38" t="inlineStr"/>
+      <c r="AB11" s="38" t="inlineStr"/>
+      <c r="AC11" s="38" t="inlineStr"/>
+      <c r="AD11" s="38" t="inlineStr"/>
+      <c r="AE11" s="40" t="inlineStr"/>
+      <c r="AF11" s="40" t="inlineStr"/>
+      <c r="AG11" s="38" t="inlineStr"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="B12" s="6" t="n"/>
@@ -2053,37 +2008,37 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="21" t="n"/>
-      <c r="I13" s="21" t="n"/>
-      <c r="J13" s="21" t="n"/>
-      <c r="K13" s="21" t="n"/>
-      <c r="L13" s="21" t="n"/>
-      <c r="M13" s="21" t="n"/>
-      <c r="N13" s="21" t="n"/>
-      <c r="O13" s="21" t="n"/>
-      <c r="P13" s="21" t="n"/>
-      <c r="Q13" s="21" t="n"/>
-      <c r="R13" s="21" t="n"/>
-      <c r="S13" s="21" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
-      <c r="X13" s="21" t="n"/>
-      <c r="Y13" s="21" t="n"/>
-      <c r="Z13" s="21" t="n"/>
-      <c r="AA13" s="21" t="n"/>
-      <c r="AB13" s="21" t="n"/>
-      <c r="AC13" s="21" t="n"/>
-      <c r="AD13" s="21" t="n"/>
-      <c r="AE13" s="21" t="n"/>
-      <c r="AF13" s="21" t="n"/>
-      <c r="AG13" s="21" t="n"/>
+      <c r="C13" s="21" t="inlineStr"/>
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+      <c r="I13" s="21" t="inlineStr"/>
+      <c r="J13" s="21" t="inlineStr"/>
+      <c r="K13" s="21" t="inlineStr"/>
+      <c r="L13" s="21" t="inlineStr"/>
+      <c r="M13" s="21" t="inlineStr"/>
+      <c r="N13" s="21" t="inlineStr"/>
+      <c r="O13" s="21" t="inlineStr"/>
+      <c r="P13" s="21" t="inlineStr"/>
+      <c r="Q13" s="21" t="inlineStr"/>
+      <c r="R13" s="21" t="inlineStr"/>
+      <c r="S13" s="21" t="inlineStr"/>
+      <c r="T13" s="21" t="inlineStr"/>
+      <c r="U13" s="21" t="inlineStr"/>
+      <c r="V13" s="21" t="inlineStr"/>
+      <c r="W13" s="21" t="inlineStr"/>
+      <c r="X13" s="21" t="inlineStr"/>
+      <c r="Y13" s="21" t="inlineStr"/>
+      <c r="Z13" s="21" t="inlineStr"/>
+      <c r="AA13" s="21" t="inlineStr"/>
+      <c r="AB13" s="21" t="inlineStr"/>
+      <c r="AC13" s="21" t="inlineStr"/>
+      <c r="AD13" s="21" t="inlineStr"/>
+      <c r="AE13" s="21" t="inlineStr"/>
+      <c r="AF13" s="21" t="inlineStr"/>
+      <c r="AG13" s="21" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="6" t="n"/>
@@ -2127,7 +2082,7 @@
       </c>
     </row>
     <row r="16" ht="185.25" customHeight="1">
-      <c r="B16" s="32" t="inlineStr"/>
+      <c r="B16" s="41" t="inlineStr"/>
     </row>
     <row r="17" ht="23.25" customHeight="1"/>
     <row r="18" ht="21" customHeight="1">
@@ -2173,8 +2128,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -2128,8 +2128,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -2128,8 +2128,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -1746,7 +1746,11 @@
       <c r="E6" s="24" t="inlineStr"/>
       <c r="F6" s="24" t="inlineStr"/>
       <c r="G6" s="24" t="inlineStr"/>
-      <c r="H6" s="24" t="inlineStr"/>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="24" t="inlineStr"/>
       <c r="J6" s="24" t="inlineStr"/>
       <c r="K6" s="24" t="inlineStr"/>
@@ -1787,7 +1791,11 @@
       <c r="E7" s="24" t="inlineStr"/>
       <c r="F7" s="24" t="inlineStr"/>
       <c r="G7" s="24" t="inlineStr"/>
-      <c r="H7" s="24" t="inlineStr"/>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="24" t="inlineStr"/>
       <c r="J7" s="24" t="inlineStr"/>
       <c r="K7" s="24" t="inlineStr"/>
@@ -1828,7 +1836,11 @@
       <c r="E8" s="24" t="inlineStr"/>
       <c r="F8" s="24" t="inlineStr"/>
       <c r="G8" s="24" t="inlineStr"/>
-      <c r="H8" s="24" t="inlineStr"/>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="24" t="inlineStr"/>
       <c r="J8" s="24" t="inlineStr"/>
       <c r="K8" s="24" t="inlineStr"/>
@@ -1869,7 +1881,11 @@
       <c r="E9" s="24" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr"/>
       <c r="G9" s="24" t="inlineStr"/>
-      <c r="H9" s="24" t="inlineStr"/>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="24" t="inlineStr"/>
       <c r="J9" s="24" t="inlineStr"/>
       <c r="K9" s="24" t="inlineStr"/>
@@ -1910,7 +1926,11 @@
       <c r="E10" s="24" t="inlineStr"/>
       <c r="F10" s="24" t="inlineStr"/>
       <c r="G10" s="24" t="inlineStr"/>
-      <c r="H10" s="24" t="inlineStr"/>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="24" t="inlineStr"/>
       <c r="J10" s="24" t="inlineStr"/>
       <c r="K10" s="24" t="inlineStr"/>
@@ -1945,7 +1965,11 @@
       <c r="E11" s="38" t="inlineStr"/>
       <c r="F11" s="38" t="inlineStr"/>
       <c r="G11" s="38" t="inlineStr"/>
-      <c r="H11" s="38" t="inlineStr"/>
+      <c r="H11" s="40" t="inlineStr">
+        <is>
+          <t>พนารัตน์</t>
+        </is>
+      </c>
       <c r="I11" s="38" t="inlineStr"/>
       <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
@@ -2128,8 +2152,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -330,7 +330,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -434,6 +434,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2037,7 +2040,11 @@
       <c r="E13" s="21" t="inlineStr"/>
       <c r="F13" s="21" t="inlineStr"/>
       <c r="G13" s="21" t="inlineStr"/>
-      <c r="H13" s="21" t="inlineStr"/>
+      <c r="H13" s="42" t="inlineStr">
+        <is>
+          <t>ณรงค์ชัย</t>
+        </is>
+      </c>
       <c r="I13" s="21" t="inlineStr"/>
       <c r="J13" s="21" t="inlineStr"/>
       <c r="K13" s="21" t="inlineStr"/>
@@ -2152,8 +2159,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -1754,7 +1754,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="24" t="inlineStr"/>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="24" t="inlineStr"/>
       <c r="K6" s="24" t="inlineStr"/>
       <c r="L6" s="24" t="inlineStr"/>
@@ -1799,7 +1803,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr"/>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="24" t="inlineStr"/>
       <c r="K7" s="24" t="inlineStr"/>
       <c r="L7" s="24" t="inlineStr"/>
@@ -1844,7 +1852,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr"/>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="24" t="inlineStr"/>
       <c r="K8" s="24" t="inlineStr"/>
       <c r="L8" s="24" t="inlineStr"/>
@@ -1889,7 +1901,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="24" t="inlineStr"/>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="24" t="inlineStr"/>
       <c r="K9" s="24" t="inlineStr"/>
       <c r="L9" s="24" t="inlineStr"/>
@@ -1934,7 +1950,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr"/>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="24" t="inlineStr"/>
       <c r="K10" s="24" t="inlineStr"/>
       <c r="L10" s="24" t="inlineStr"/>
@@ -1973,7 +1993,11 @@
           <t>พนารัตน์</t>
         </is>
       </c>
-      <c r="I11" s="38" t="inlineStr"/>
+      <c r="I11" s="40" t="inlineStr">
+        <is>
+          <t>พนารัตน์</t>
+        </is>
+      </c>
       <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
       <c r="L11" s="38" t="inlineStr"/>
@@ -2159,8 +2183,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="P11:P12"/>
     <mergeCell ref="B16:AG16"/>
-    <mergeCell ref="P11:P12"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>

--- a/FM-MN-07_QC-08.xlsx
+++ b/FM-MN-07_QC-08.xlsx
@@ -1759,7 +1759,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="24" t="inlineStr"/>
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="24" t="inlineStr"/>
       <c r="L6" s="24" t="inlineStr"/>
       <c r="M6" s="24" t="inlineStr"/>
@@ -1808,7 +1812,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="24" t="inlineStr"/>
+      <c r="J7" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="24" t="inlineStr"/>
       <c r="L7" s="24" t="inlineStr"/>
       <c r="M7" s="24" t="inlineStr"/>
@@ -1857,7 +1865,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="24" t="inlineStr"/>
+      <c r="J8" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="24" t="inlineStr"/>
       <c r="L8" s="24" t="inlineStr"/>
       <c r="M8" s="24" t="inlineStr"/>
@@ -1906,7 +1918,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="24" t="inlineStr"/>
+      <c r="J9" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="24" t="inlineStr"/>
       <c r="L9" s="24" t="inlineStr"/>
       <c r="M9" s="24" t="inlineStr"/>
@@ -1955,7 +1971,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="24" t="inlineStr"/>
+      <c r="J10" s="24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="24" t="inlineStr"/>
       <c r="L10" s="24" t="inlineStr"/>
       <c r="M10" s="24" t="inlineStr"/>
@@ -1998,7 +2018,11 @@
           <t>พนารัตน์</t>
         </is>
       </c>
-      <c r="J11" s="38" t="inlineStr"/>
+      <c r="J11" s="40" t="inlineStr">
+        <is>
+          <t>พนารัตน์</t>
+        </is>
+      </c>
       <c r="K11" s="38" t="inlineStr"/>
       <c r="L11" s="38" t="inlineStr"/>
       <c r="M11" s="38" t="inlineStr"/>
@@ -2183,8 +2207,8 @@
     <mergeCell ref="Y11:Y12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="B16:AG16"/>
     <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AC18:AG18"/>
     <mergeCell ref="K11:K12"/>
